--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131990424</v>
       </c>
       <c r="B3" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131990418</v>
       </c>
       <c r="B4" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131990420</v>
       </c>
       <c r="B7" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97344</v>
+        <v>97347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131990424</v>
       </c>
       <c r="B3" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131990418</v>
       </c>
       <c r="B4" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131990417</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131990415</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131990420</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131990424</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131990418</v>
       </c>
       <c r="B4" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131990417</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>131990415</v>
       </c>
       <c r="B6" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131990420</v>
       </c>
       <c r="B7" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97355</v>
+        <v>97365</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>131990424</v>
       </c>
       <c r="B3" t="n">
-        <v>96346</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>131990418</v>
       </c>
       <c r="B4" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>131990420</v>
       </c>
       <c r="B7" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97365</v>
+        <v>97367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97367</v>
+        <v>97368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97368</v>
+        <v>97370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -1302,7 +1302,7 @@
         <v>132158167</v>
       </c>
       <c r="B8" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>132158162</v>
       </c>
       <c r="B9" t="n">
-        <v>97370</v>
+        <v>97371</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102938511</v>
+        <v>131990418</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bengtsfors, Dls</t>
+          <t>Hagetjärnet, 150-200 m söder om, Alltorp, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>338873.2518792834</v>
+        <v>338984</v>
       </c>
       <c r="R2" t="n">
-        <v>6525731.02669963</v>
+        <v>6525820</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,48 +756,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gammal barrskog på blockrik mark.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131990424</v>
+        <v>131990420</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>338875</v>
+        <v>338967</v>
       </c>
       <c r="R3" t="n">
-        <v>6525853</v>
+        <v>6525831</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131990418</v>
+        <v>132158167</v>
       </c>
       <c r="B4" t="n">
-        <v>97358</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>338984</v>
+        <v>338890</v>
       </c>
       <c r="R4" t="n">
-        <v>6525820</v>
+        <v>6525841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +964,11 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Gammal barrskog på blockrik mark.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -993,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131990417</v>
+        <v>132158162</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>97444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbtrådmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscocephaloziopsis catenulata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>338918</v>
+        <v>338890</v>
       </c>
       <c r="R5" t="n">
-        <v>6525834</v>
+        <v>6525841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1078,6 +1071,11 @@
       <c r="AI5" t="inlineStr">
         <is>
           <t>Gammal barrskog på blockrik mark.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1095,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131990415</v>
+        <v>102938511</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,37 +1104,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagetjärnet, 150-200 m söder om, Alltorp, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>338896</v>
+        <v>338873</v>
       </c>
       <c r="R6" t="n">
-        <v>6525889</v>
+        <v>6525732</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,12 +1160,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,53 +1186,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Gammal barrskog på blockrik mark.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131990420</v>
+        <v>131990424</v>
       </c>
       <c r="B7" t="n">
-        <v>97358</v>
+        <v>96423</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>338967</v>
+        <v>338875</v>
       </c>
       <c r="R7" t="n">
-        <v>6525831</v>
+        <v>6525853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,32 +1304,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132158167</v>
+        <v>131990417</v>
       </c>
       <c r="B8" t="n">
-        <v>97362</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1339,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>338890</v>
+        <v>338918</v>
       </c>
       <c r="R8" t="n">
-        <v>6525841</v>
+        <v>6525834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,11 +1389,6 @@
       <c r="AI8" t="inlineStr">
         <is>
           <t>Gammal barrskog på blockrik mark.</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1406,48 +1406,59 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132158162</v>
+        <v>102940398</v>
       </c>
       <c r="B9" t="n">
-        <v>97371</v>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>291</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stubbtrådmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscocephaloziopsis catenulata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) Váňa &amp; L.Söderstr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagetjärnet, 150-200 m söder om, Alltorp, Dls</t>
+          <t>Bengtsfors, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>338890</v>
+        <v>338742</v>
       </c>
       <c r="R9" t="n">
-        <v>6525841</v>
+        <v>6525854</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1471,12 +1482,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2022-08-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1487,29 +1508,121 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal barrskog på blockrik mark.</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131990415</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hagetjärnet, 150-200 m söder om, Alltorp, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>338896</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6525889</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ödskölt</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal barrskog på blockrik mark.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Leif Appelgren</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Leif Appelgren</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29215-2022 artfynd.xlsx
+++ b/artfynd/A 29215-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131990418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131990420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132158167</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132158162</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102938511</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131990424</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131990417</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102940398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1623,8 +1668,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131990415</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>